--- a/genie_assessment/temp/assessment_outputs/genie_scorecard_brz_dev.xlsx
+++ b/genie_assessment/temp/assessment_outputs/genie_scorecard_brz_dev.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,11 +50,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C6500"/>
     </font>
   </fonts>
   <fills count="7">
@@ -81,12 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,14 +137,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -736,11 +736,11 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="8" t="inlineStr"/>
       <c r="D13" s="8" t="inlineStr"/>
@@ -800,17 +800,17 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>4 / 5 tables registered</t>
+          <t>2 / 2 tables registered</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Register 1 missing tables</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
@@ -852,7 +852,7 @@
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
@@ -879,14 +879,14 @@
           <t>Blocker</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>4 PKs / 1 FKs defined</t>
+          <t>2 PKs / 1 FKs defined</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -906,14 +906,14 @@
           <t>Desirable</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>4 tables in scope</t>
+          <t>2 tables in scope</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -950,14 +950,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Layer 1 Rollup</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>YELLOW</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1034,32 +1034,78 @@
       <c r="A27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>¿Cuántas órdenes existen por segmento?</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>El número de órdenes por segmento de mercado varía según los datos. Por ejemplo, el segmento 'AUTOMOBILE' podría tener 29,752 órdenes, 'BUILDING' 27,631, 'FURNITURE' 28,144, 'HOUSEHOLD' 28,823 y 'MACHINERY' 27,650 (valores hipotéticos ilustrativos). La consulta SQL proporcionada calculará los valores reales.</t>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Cuáles son las ventas por producto?</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Las ventas netas por producto (identificado por product_id) muestran el total acumulado de cada producto. Por ejemplo, el producto con product_id 1 podría tener ventas netas de $X, el producto 2 de $Y, etc. Sin embargo, no es posible mostrar los nombres de los productos ya que no existe una tabla de dimensión de productos en el esquema disponible.</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
       <c r="F27" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>The fact_sales_demo_genie table contains product_id, gross_sales, net_sales, discount, and quantity, which are sufficient to aggregate sales by product. However, the question is marked PARTIAL for two reasons: (1) there is no dim_product table in the schema, so product names cannot be displayed — only numeric IDs are available; (2) the term 'ventas' is ambiguous (gross vs. net vs. units). The SQL provided returns all three metrics to cover the ambiguity, but a business user would need to confirm which measure is relevant. If a dim_product table were added to the catalog, the answer could be upgraded to YES.</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    product_id,
+    SUM(gross_sales)  AS total_gross_sales,
+    SUM(discount)     AS total_discount,
+    SUM(net_sales)    AS total_net_sales,
+    SUM(quantity)     AS total_quantity
+FROM
+    brz_dev.default.fact_sales_demo_genie
+GROUP BY
+    product_id
+ORDER BY
+    total_net_sales DESC;</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Cuántas órdenes existen por segmento?</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr"/>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>El número de órdenes por segmento de mercado varía según los datos. Por ejemplo, el segmento 'AUTOMOBILE' podría tener 29,000 órdenes, 'BUILDING' 27,500, 'FURNITURE' 28,000, 'HOUSEHOLD' 28,500 y 'MACHINERY' 27,000 (valores hipotéticos). Para obtener los valores reales se debe ejecutar la consulta SQL correspondiente.</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>La pregunta solicita el conteo de órdenes agrupadas por segmento de mercado. La tabla de hechos 'fact_sales_demo_genie' contiene el campo 'order_id' (identificador de orden) y 'customer_id' (para enlazar con el cliente). La dimensión 'dim_customer_demo_genie' contiene el campo 'market_segment'. Mediante un JOIN entre ambas tablas por 'customer_id' y usando COUNT(DISTINCT order_id) agrupado por 'market_segment', se puede responder la pregunta de forma completa y precisa. No hay ambigüedad ni datos faltantes.</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita el conteo de órdenes agrupadas por segmento de mercado. La tabla fact_sales_demo_genie contiene el campo order_id (que puede repetirse por línea de producto) y customer_id. La tabla dim_customer_demo_genie contiene el campo market_segment y customer_id como llave primaria. Uniendo ambas tablas por customer_id y aplicando COUNT(DISTINCT order_id) agrupado por market_segment se responde completamente la pregunta. Se usa DISTINCT en order_id porque una orden puede tener múltiples líneas de producto y no queremos contarla más de una vez.</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>SELECT
     c.market_segment,
@@ -1075,198 +1121,222 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Layer 2 Rollup</t>
         </is>
       </c>
-      <c r="B28" s="14">
-        <f>IFERROR(COUNTIF(E27:E27, "YES")/COUNTA(E27:E27), 0)</f>
+      <c r="B29" s="14">
+        <f>IFERROR(COUNTIF(E27:E28, "YES")/COUNTA(E27:E28), 0)</f>
         <v/>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>% of tested questions with Match = YES (informational — not blended into Layer 1's gate)</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="8" t="inlineStr"/>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="12" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>LAYER 3 — QUERY LIBRARY READINESS (auto-scanned)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Query / View Name</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Confidence (1–10)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Maps to Q#</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Key Issues</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Cleanup Needed?</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Layer 3 Rollup</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>% of scanned queries that are GOOD_CANDIDATE (informational)</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr"/>
-      <c r="F32" s="12" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr"/>
+      <c r="E33" s="11" t="inlineStr"/>
+      <c r="F33" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>LAYER 4 — TOP USE CASES &amp; VALUE (manual, scored at the workshop)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Q#</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Business Question</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Data Exists &amp; in UC (1–3)</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Question Clearly Defined (1–3)</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Acceptance Criteria Written (1–3)</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Business Owner Available (1–3)</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>SQL Deterministic (1–3)</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Est. Business Impact (1–3)</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>Total (/18)</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="K35" s="6" t="inlineStr">
+      <c r="K36" s="6" t="inlineStr">
         <is>
           <t>Value / Workforce Impact Notes (manual)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="n">
+    <row r="37">
+      <c r="A37" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>¿Cuántas órdenes existen por segmento?</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Cuáles son las ventas por producto?</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8">
+        <f>SUM(C37:H37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="8" t="inlineStr"/>
+      <c r="K37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Cuántas órdenes existen por segmento?</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr"/>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8">
-        <f>SUM(C36:H36)</f>
+      <c r="D38" s="8" t="inlineStr"/>
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr"/>
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8">
+        <f>SUM(C38:H38)</f>
         <v/>
       </c>
-      <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="12" t="inlineStr"/>
+      <c r="J38" s="8" t="inlineStr"/>
+      <c r="K38" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B29">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.8</formula>
     </cfRule>
@@ -1278,7 +1348,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+  <conditionalFormatting sqref="B33">
     <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.8</formula>
     </cfRule>

--- a/genie_assessment/temp/assessment_outputs/genie_scorecard_brz_dev.xlsx
+++ b/genie_assessment/temp/assessment_outputs/genie_scorecard_brz_dev.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,12 +52,8 @@
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C6500"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,11 +78,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,9 +133,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -555,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -660,7 +648,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +728,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C13" s="8" t="inlineStr"/>
       <c r="D13" s="8" t="inlineStr"/>
@@ -805,7 +793,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2 / 2 tables registered</t>
+          <t>4 / 4 tables registered</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -886,7 +874,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2 PKs / 1 FKs defined</t>
+          <t>4 PKs / 1 FKs defined</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -913,7 +901,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2 tables in scope</t>
+          <t>4 tables in scope</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1036,43 +1024,42 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Cuáles son las ventas por producto?</t>
+          <t>¿Cuáles fueron las ventas netas por año?</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr"/>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Las ventas netas por producto (identificado por product_id) muestran el total acumulado de cada producto. Por ejemplo, el producto con product_id 1 podría tener ventas netas de $X, el producto 2 de $Y, etc. Sin embargo, no es posible mostrar los nombres de los productos ya que no existe una tabla de dimensión de productos en el esquema disponible.</t>
+          <t>Las ventas netas por año se pueden calcular sumando el campo net_sales de la tabla de hechos agrupado por el año de la dimensión de fechas. Por ejemplo: Año 2021: $X, Año 2022: $Y, Año 2023: $Z.</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
       <c r="F27" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+        <v>10</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>The fact_sales_demo_genie table contains product_id, gross_sales, net_sales, discount, and quantity, which are sufficient to aggregate sales by product. However, the question is marked PARTIAL for two reasons: (1) there is no dim_product table in the schema, so product names cannot be displayed — only numeric IDs are available; (2) the term 'ventas' is ambiguous (gross vs. net vs. units). The SQL provided returns all three metrics to cover the ambiguity, but a business user would need to confirm which measure is relevant. If a dim_product table were added to the catalog, the answer could be upgraded to YES.</t>
+          <t>La pregunta solicita las ventas netas agrupadas por año. La tabla fact_sales_demo_genie contiene el campo net_sales (ventas netas) y la clave foránea date_id. La tabla dim_date_demo_genie contiene el campo year que permite agrupar por año. Un simple JOIN entre ambas tablas y una agregación SUM sobre net_sales agrupada por year es suficiente para responder la pregunta de forma completa y sin ambigüedades.</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
           <t>SELECT
-    product_id,
-    SUM(gross_sales)  AS total_gross_sales,
-    SUM(discount)     AS total_discount,
-    SUM(net_sales)    AS total_net_sales,
-    SUM(quantity)     AS total_quantity
+    d.year,
+    SUM(f.net_sales) AS total_net_sales
 FROM
-    brz_dev.default.fact_sales_demo_genie
+    brz_dev.default.fact_sales_demo_genie f
+    JOIN brz_dev.default.dim_date_demo_genie d
+        ON f.date_id = d.date_id
 GROUP BY
-    product_id
+    d.year
 ORDER BY
-    total_net_sales DESC;</t>
+    d.year ASC;</t>
         </is>
       </c>
     </row>
@@ -1082,13 +1069,13 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Cuántas órdenes existen por segmento?</t>
+          <t>¿Cuál es el top 5 de productos con mayores ventas?</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr"/>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>El número de órdenes por segmento de mercado varía según los datos. Por ejemplo, el segmento 'AUTOMOBILE' podría tener 29,000 órdenes, 'BUILDING' 27,500, 'FURNITURE' 28,000, 'HOUSEHOLD' 28,500 y 'MACHINERY' 27,000 (valores hipotéticos). Para obtener los valores reales se debe ejecutar la consulta SQL correspondiente.</t>
+          <t>El top 5 de productos con mayores ventas netas serían los 5 productos con mayor suma de net_sales en la tabla de hechos, identificados por su nombre en dim_product_demo_genie. Por ejemplo: Producto A ($5,200,000), Producto B ($4,800,000), Producto C ($4,100,000), Producto D ($3,750,000), Producto E ($3,200,000).</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -1102,241 +1089,818 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita el conteo de órdenes agrupadas por segmento de mercado. La tabla fact_sales_demo_genie contiene el campo order_id (que puede repetirse por línea de producto) y customer_id. La tabla dim_customer_demo_genie contiene el campo market_segment y customer_id como llave primaria. Uniendo ambas tablas por customer_id y aplicando COUNT(DISTINCT order_id) agrupado por market_segment se responde completamente la pregunta. Se usa DISTINCT en order_id porque una orden puede tener múltiples líneas de producto y no queremos contarla más de una vez.</t>
+          <t>La pregunta solicita el top 5 de productos con mayores ventas. La tabla fact_sales_demo_genie contiene las métricas de ventas (net_sales, gross_sales, quantity) y la clave foránea product_id. La tabla dim_product_demo_genie contiene el nombre descriptivo del producto. Con un simple JOIN, agregación por producto y ordenamiento descendente por ventas netas (net_sales), se puede responder la pregunta. Se usa net_sales como métrica principal de ventas ya que representa el valor real después de descuentos, aunque también se incluye gross_sales para referencia. La pregunta es directamente respondible con los datos disponibles.</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
           <t>SELECT
-    c.market_segment,
-    COUNT(DISTINCT f.order_id) AS total_orders
+    p.product_id,
+    p.product_name,
+    p.brand,
+    p.product_type,
+    SUM(f.net_sales) AS total_net_sales,
+    SUM(f.gross_sales) AS total_gross_sales,
+    SUM(f.quantity) AS total_quantity
+FROM
+    brz_dev.default.fact_sales_demo_genie f
+    JOIN brz_dev.default.dim_product_demo_genie p
+        ON f.product_id = p.product_id
+GROUP BY
+    p.product_id,
+    p.product_name,
+    p.brand,
+    p.product_type
+ORDER BY
+    total_net_sales DESC
+LIMIT 5;</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuántas unidades se vendieron por producto?</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr"/>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Las unidades vendidas por producto se obtienen sumando la columna 'quantity' de la tabla de hechos agrupada por producto. Por ejemplo: Producto A → 1,200 unidades, Producto B → 850 unidades, Producto C → 2,300 unidades, etc.</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita la suma de unidades vendidas agrupadas por producto. La tabla de hechos 'fact_sales_demo_genie' contiene la columna 'quantity' (unidades vendidas) y la llave foránea 'product_id'. La dimensión 'dim_product_demo_genie' contiene los atributos descriptivos del producto (nombre, marca, tipo). Un simple JOIN entre ambas tablas y un GROUP BY sobre product_id/product_name con SUM(quantity) responde completamente la pregunta. No hay ambigüedad ni datos faltantes.</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    p.product_id,
+    p.product_name,
+    p.brand,
+    p.product_type,
+    SUM(f.quantity) AS total_units_sold
+FROM
+    brz_dev.default.fact_sales_demo_genie f
+    JOIN brz_dev.default.dim_product_demo_genie p
+        ON f.product_id = p.product_id
+GROUP BY
+    p.product_id,
+    p.product_name,
+    p.brand,
+    p.product_type
+ORDER BY
+    total_units_sold DESC;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuál es el descuento promedio por cliente?</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr"/>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>El descuento promedio por cliente varía según cada uno. Por ejemplo, el cliente 'Empresa ABC' tiene un descuento promedio de $150.00 por línea de venta, mientras que 'Distribuidora XYZ' tiene un promedio de $85.50. La consulta devuelve el promedio del campo 'discount' agrupado por cada cliente.</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita el descuento promedio por cliente. La tabla de hechos 'fact_sales_demo_genie' contiene la columna 'discount' (descuento aplicado a cada línea de venta) y 'customer_id' como llave foránea. La dimensión 'dim_customer_demo_genie' aporta el nombre del cliente. Con un simple JOIN y un AVG(discount) agrupado por customer_id y customer_name, la pregunta queda completamente respondida. No hay ambigüedad en la definición del descuento promedio ya que existe una columna explícita para ello.</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    c.customer_id,
+    c.customer_name,
+    AVG(f.discount) AS avg_discount
 FROM
     brz_dev.default.fact_sales_demo_genie f
     JOIN brz_dev.default.dim_customer_demo_genie c
         ON f.customer_id = c.customer_id
 GROUP BY
-    c.market_segment
+    c.customer_id,
+    c.customer_name
 ORDER BY
-    total_orders DESC;</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+    avg_discount DESC;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuántas órdenes se realizaron en total?</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>El total de órdenes realizadas se obtiene contando los valores distintos de order_id en la tabla de hechos de ventas. Por ejemplo, si existen 15,000 valores únicos de order_id, entonces se realizaron 15,000 órdenes en total.</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita el conteo total de órdenes. La tabla fact_sales_demo_genie contiene la columna order_id, que identifica cada orden. Dado que una orden puede tener múltiples líneas de producto (y por tanto múltiples filas con el mismo order_id), se debe usar COUNT(DISTINCT order_id) para obtener el número real de órdenes únicas. No se requieren joins adicionales ni información de otras tablas para responder esta pregunta.</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(DISTINCT order_id) AS total_orders
+FROM brz_dev.default.fact_sales_demo_genie;</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuáles son los 10 clientes con mayores ventas brutas?</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr"/>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Los 10 clientes con mayores ventas brutas son aquellos cuya suma de gross_sales en la tabla de hechos es más alta. Por ejemplo, el cliente con mayor venta bruta podría ser 'Cliente A' con $X millones, seguido de 'Cliente B' con $Y millones, y así sucesivamente hasta completar el top 10.</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr"/>
+      <c r="F32" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita los 10 clientes con mayores ventas brutas. La tabla fact_sales_demo_genie contiene la columna gross_sales y customer_id, y la tabla dim_customer_demo_genie contiene el nombre del cliente (customer_name) junto con su identificador (customer_id). Con un simple JOIN entre ambas tablas, una agregación SUM sobre gross_sales agrupada por cliente, y un ORDER BY DESC con LIMIT 10, se puede responder la pregunta de forma completa y precisa. No hay ambigüedad ni datos faltantes.</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    c.customer_id,
+    c.customer_name,
+    SUM(f.gross_sales) AS total_gross_sales
+FROM
+    brz_dev.default.fact_sales_demo_genie f
+    JOIN brz_dev.default.dim_customer_demo_genie c
+        ON f.customer_id = c.customer_id
+GROUP BY
+    c.customer_id,
+    c.customer_name
+ORDER BY
+    total_gross_sales DESC
+LIMIT 10;</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuál es la diferencia entre ventas brutas y ventas netas por año?</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr"/>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>La diferencia entre ventas brutas y ventas netas (es decir, el total de descuentos aplicados) por año sería, por ejemplo: en 2022 las ventas brutas fueron $5,000,000, las ventas netas $4,500,000 y la diferencia (descuentos) fue de $500,000; en 2023 las ventas brutas fueron $6,200,000, las ventas netas $5,600,000 y la diferencia fue de $600,000. (Los valores exactos dependen de los datos reales en la tabla.)</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita la diferencia entre ventas brutas (gross_sales) y ventas netas (net_sales) agrupada por año. Ambas métricas existen directamente en la tabla de hechos 'fact_sales_demo_genie'. El año se obtiene haciendo un JOIN con 'dim_date_demo_genie' usando la clave 'date_id'. La diferencia entre ambas columnas equivale al descuento total aplicado, que también está disponible en la columna 'discount'. No hay ambigüedad ni datos faltantes; la pregunta es completamente respondible con las tablas disponibles.</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    d.year,
+    SUM(f.gross_sales)                        AS total_gross_sales,
+    SUM(f.net_sales)                           AS total_net_sales,
+    SUM(f.gross_sales) - SUM(f.net_sales)      AS difference_gross_vs_net,
+    SUM(f.discount)                            AS total_discount
+FROM brz_dev.default.fact_sales_demo_genie f
+JOIN brz_dev.default.dim_date_demo_genie d
+    ON f.date_id = d.date_id
+GROUP BY d.year
+ORDER BY d.year;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuántas unidades se vendieron por mes en el último año?</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr"/>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>En el último año (2024, por ejemplo), las unidades vendidas por mes fueron: Enero: 12,500 unidades, Febrero: 11,800 unidades, Marzo: 13,200 unidades, ... (los valores exactos dependerán de los datos reales en la tabla).</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita el total de unidades vendidas (quantity) agrupadas por mes, restringidas al último año disponible. La tabla de hechos 'fact_sales_demo_genie' contiene la columna 'quantity' (unidades vendidas) y 'date_id' como llave foránea hacia la dimensión de fechas. La tabla 'dim_date_demo_genie' provee las columnas 'year', 'month' y 'month_name' necesarias para la agrupación mensual. El 'último año' se puede derivar dinámicamente usando MAX(year) sobre la dimensión de fechas, lo cual es una derivación SQL estándar. No hay ambigüedad en la pregunta ni datos faltantes.</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    d.year,
+    d.month,
+    d.month_name,
+    SUM(f.quantity) AS total_units_sold
+FROM
+    brz_dev.default.fact_sales_demo_genie f
+    JOIN brz_dev.default.dim_date_demo_genie d
+        ON f.date_id = d.date_id
+WHERE
+    d.year = (
+        SELECT MAX(year)
+        FROM brz_dev.default.dim_date_demo_genie
+    )
+GROUP BY
+    d.year,
+    d.month,
+    d.month_name
+ORDER BY
+    d.month ASC;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>¿Qué productos tienen un descuento promedio mayor al 10%?</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr"/>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Los productos con un descuento promedio mayor al 10% son aquellos cuyo promedio de la columna 'discount' en la tabla de hechos supera el 10% del valor bruto de venta (gross_sales). Por ejemplo, podrían ser productos como 'Producto A' con un descuento promedio del 12%, 'Producto B' con 15%, etc. La lista exacta depende de los datos reales.</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita productos cuyo descuento promedio supere el 10%. La tabla 'fact_sales_demo_genie' contiene las columnas 'discount' y 'gross_sales', lo que permite calcular el porcentaje de descuento promedio por producto (discount / gross_sales * 100). La tabla 'dim_product_demo_genie' proporciona los atributos descriptivos del producto (nombre, marca, tipo, fabricante). Se asume que el '10%' se refiere al porcentaje del descuento respecto al valor bruto de venta, que es la interpretación más estándar en contextos comerciales. El JOIN entre ambas tablas se realiza mediante product_id. La consulta agrupa por producto, calcula el porcentaje promedio de descuento y filtra aquellos que superan el 10%.</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    p.product_id,
+    p.product_name,
+    p.brand,
+    p.product_type,
+    p.manufacturer,
+    AVG(f.discount) AS avg_discount,
+    AVG(f.gross_sales) AS avg_gross_sales,
+    AVG(f.discount / NULLIF(f.gross_sales, 0)) * 100 AS avg_discount_pct
+FROM
+    brz_dev.default.fact_sales_demo_genie f
+    JOIN brz_dev.default.dim_product_demo_genie p
+        ON f.product_id = p.product_id
+GROUP BY
+    p.product_id,
+    p.product_name,
+    p.brand,
+    p.product_type,
+    p.manufacturer
+HAVING
+    AVG(f.discount / NULLIF(f.gross_sales, 0)) * 100 &gt; 10
+ORDER BY
+    avg_discount_pct DESC;</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuál es el ingreso neto promedio por orden?</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr"/>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>El ingreso neto promedio por orden es el resultado de dividir la suma total de net_sales entre el número de órdenes únicas (order_id). Por ejemplo, si la suma total de net_sales es $10,000,000 y existen 500 órdenes únicas, el ingreso neto promedio por orden sería $20,000.</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr"/>
+      <c r="F36" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>La pregunta solicita el ingreso neto promedio por orden. La tabla fact_sales_demo_genie contiene tanto 'net_sales' (valor neto de la venta) como 'order_id' (identificador de la orden). Dado que una orden puede tener múltiples líneas de producto, el ingreso neto por orden se calcula sumando net_sales agrupado por order_id, y luego promediando esos totales. Esto es equivalente a dividir la suma total de net_sales entre el número de órdenes únicas (COUNT DISTINCT order_id). No se requieren joins adicionales ni existe ambigüedad en la definición del indicador.</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+  SUM(net_sales) / COUNT(DISTINCT order_id) AS avg_net_sales_per_order
+FROM
+  brz_dev.default.fact_sales_demo_genie;</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Layer 2 Rollup</t>
         </is>
       </c>
-      <c r="B29" s="14">
-        <f>IFERROR(COUNTIF(E27:E28, "YES")/COUNTA(E27:E28), 0)</f>
+      <c r="B37" s="13">
+        <f>IFERROR(COUNTIF(E27:E36, "YES")/COUNTA(E27:E36), 0)</f>
         <v/>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>% of tested questions with Match = YES (informational — not blended into Layer 1's gate)</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="11" t="inlineStr"/>
-      <c r="I29" s="11" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>LAYER 3 — QUERY LIBRARY READINESS (auto-scanned)</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Query / View Name</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Confidence (1–10)</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Maps to Q#</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Key Issues</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Cleanup Needed?</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Layer 3 Rollup</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>% of scanned queries that are GOOD_CANDIDATE (informational)</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr"/>
-      <c r="E33" s="11" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>LAYER 4 — TOP USE CASES &amp; VALUE (manual, scored at the workshop)</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Q#</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Business Question</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Data Exists &amp; in UC (1–3)</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Question Clearly Defined (1–3)</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria Written (1–3)</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>Business Owner Available (1–3)</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>SQL Deterministic (1–3)</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>Est. Business Impact (1–3)</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Total (/18)</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>Value / Workforce Impact Notes (manual)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Cuáles son las ventas por producto?</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="8" t="inlineStr"/>
+      <c r="D37" s="11" t="inlineStr"/>
       <c r="E37" s="8" t="inlineStr"/>
       <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8">
-        <f>SUM(C37:H37)</f>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>LAYER 3 — QUERY LIBRARY READINESS (auto-scanned)</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Query / View Name</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Confidence (1–10)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Maps to Q#</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Key Issues</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Cleanup Needed?</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Layer 3 Rollup</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>% of scanned queries that are GOOD_CANDIDATE (informational)</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr"/>
+      <c r="E41" s="11" t="inlineStr"/>
+      <c r="F41" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>LAYER 4 — TOP USE CASES &amp; VALUE (manual, scored at the workshop)</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Q#</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Business Question</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Data Exists &amp; in UC (1–3)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Question Clearly Defined (1–3)</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria Written (1–3)</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Business Owner Available (1–3)</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>SQL Deterministic (1–3)</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Est. Business Impact (1–3)</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Total (/18)</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Value / Workforce Impact Notes (manual)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuáles fueron las ventas netas por año?</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="8" t="inlineStr"/>
+      <c r="E45" s="8" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8">
+        <f>SUM(C45:H45)</f>
         <v/>
       </c>
-      <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n">
+      <c r="J45" s="8" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Cuántas órdenes existen por segmento?</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuál es el top 5 de productos con mayores ventas?</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D38" s="8" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr"/>
-      <c r="G38" s="8" t="inlineStr"/>
-      <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="8">
-        <f>SUM(C38:H38)</f>
+      <c r="D46" s="8" t="inlineStr"/>
+      <c r="E46" s="8" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr"/>
+      <c r="G46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8">
+        <f>SUM(C46:H46)</f>
         <v/>
       </c>
-      <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="11" t="inlineStr"/>
+      <c r="J46" s="8" t="inlineStr"/>
+      <c r="K46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuántas unidades se vendieron por producto?</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="8" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8">
+        <f>SUM(C47:H47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuál es el descuento promedio por cliente?</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="8" t="inlineStr"/>
+      <c r="E48" s="8" t="inlineStr"/>
+      <c r="F48" s="8" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8">
+        <f>SUM(C48:H48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="8" t="inlineStr"/>
+      <c r="K48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuántas órdenes se realizaron en total?</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="8" t="inlineStr"/>
+      <c r="E49" s="8" t="inlineStr"/>
+      <c r="F49" s="8" t="inlineStr"/>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8">
+        <f>SUM(C49:H49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="8" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuáles son los 10 clientes con mayores ventas brutas?</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="8" t="inlineStr"/>
+      <c r="E50" s="8" t="inlineStr"/>
+      <c r="F50" s="8" t="inlineStr"/>
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8">
+        <f>SUM(C50:H50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="8" t="inlineStr"/>
+      <c r="K50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuál es la diferencia entre ventas brutas y ventas netas por año?</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="8" t="inlineStr"/>
+      <c r="E51" s="8" t="inlineStr"/>
+      <c r="F51" s="8" t="inlineStr"/>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8">
+        <f>SUM(C51:H51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="8" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuántas unidades se vendieron por mes en el último año?</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="8" t="inlineStr"/>
+      <c r="E52" s="8" t="inlineStr"/>
+      <c r="F52" s="8" t="inlineStr"/>
+      <c r="G52" s="8" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="8">
+        <f>SUM(C52:H52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="8" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>¿Qué productos tienen un descuento promedio mayor al 10%?</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="8" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8">
+        <f>SUM(C53:H53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="8" t="inlineStr"/>
+      <c r="K53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>¿Cuál es el ingreso neto promedio por orden?</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="8" t="inlineStr"/>
+      <c r="E54" s="8" t="inlineStr"/>
+      <c r="F54" s="8" t="inlineStr"/>
+      <c r="G54" s="8" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="8">
+        <f>SUM(C54:H54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="8" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B29">
+  <conditionalFormatting sqref="B37">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.8</formula>
     </cfRule>
@@ -1348,7 +1912,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
+  <conditionalFormatting sqref="B41">
     <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.8</formula>
     </cfRule>

--- a/genie_assessment/temp/assessment_outputs/genie_scorecard_brz_dev.xlsx
+++ b/genie_assessment/temp/assessment_outputs/genie_scorecard_brz_dev.xlsx
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita las ventas netas agrupadas por año. La tabla fact_sales_demo_genie contiene el campo net_sales (ventas netas) y la clave foránea date_id. La tabla dim_date_demo_genie contiene el campo year que permite agrupar por año. Un simple JOIN entre ambas tablas y una agregación SUM sobre net_sales agrupada por year es suficiente para responder la pregunta de forma completa y sin ambigüedades.</t>
+          <t>La pregunta solicita las ventas netas agrupadas por año. La tabla fact_sales_demo_genie contiene el campo net_sales (ventas netas) y date_id (llave foránea hacia la dimensión de fechas). La tabla dim_date_demo_genie contiene el campo year que permite agrupar por año. Un simple JOIN entre ambas tablas y una agregación SUM sobre net_sales agrupada por year es suficiente para responder la pregunta de forma completa y sin ambigüedades.</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -1075,7 +1075,7 @@
       <c r="C28" s="11" t="inlineStr"/>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>El top 5 de productos con mayores ventas netas serían los 5 productos con mayor suma de net_sales en la tabla de hechos, identificados por su nombre en dim_product_demo_genie. Por ejemplo: Producto A ($5,200,000), Producto B ($4,800,000), Producto C ($4,100,000), Producto D ($3,750,000), Producto E ($3,200,000).</t>
+          <t>El top 5 de productos con mayores ventas netas serían los 5 productos con mayor suma de net_sales en la tabla de hechos, identificados por su nombre en dim_product_demo_genie. Por ejemplo: Producto A ($X), Producto B ($Y), Producto C ($Z), Producto D ($W), Producto E ($V).</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -1089,30 +1089,26 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita el top 5 de productos con mayores ventas. La tabla fact_sales_demo_genie contiene las métricas de ventas (net_sales, gross_sales, quantity) y la clave foránea product_id. La tabla dim_product_demo_genie contiene el nombre descriptivo del producto. Con un simple JOIN, agregación por producto y ordenamiento descendente por ventas netas (net_sales), se puede responder la pregunta. Se usa net_sales como métrica principal de ventas ya que representa el valor real después de descuentos, aunque también se incluye gross_sales para referencia. La pregunta es directamente respondible con los datos disponibles.</t>
+          <t>La pregunta solicita el top 5 de productos con mayores ventas. La tabla fact_sales_demo_genie contiene las columnas net_sales y gross_sales que representan el valor de ventas, y product_id como llave foránea hacia dim_product_demo_genie, que contiene el nombre del producto. Con un simple JOIN, GROUP BY y ORDER BY DESC con LIMIT 5 se puede responder la pregunta. Se utiliza net_sales como métrica principal de ventas (valor después de descuento), que es la medida más representativa del ingreso real. La pregunta es completamente respondible con los datos disponibles.</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
           <t>SELECT
-    p.product_id,
     p.product_name,
     p.brand,
     p.product_type,
     SUM(f.net_sales) AS total_net_sales,
     SUM(f.gross_sales) AS total_gross_sales,
     SUM(f.quantity) AS total_quantity
-FROM
-    brz_dev.default.fact_sales_demo_genie f
-    JOIN brz_dev.default.dim_product_demo_genie p
-        ON f.product_id = p.product_id
+FROM brz_dev.default.fact_sales_demo_genie f
+JOIN brz_dev.default.dim_product_demo_genie p
+    ON f.product_id = p.product_id
 GROUP BY
-    p.product_id,
     p.product_name,
     p.brand,
     p.product_type
-ORDER BY
-    total_net_sales DESC
+ORDER BY total_net_sales DESC
 LIMIT 5;</t>
         </is>
       </c>
@@ -1129,7 +1125,7 @@
       <c r="C29" s="11" t="inlineStr"/>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Las unidades vendidas por producto se obtienen sumando la columna 'quantity' de la tabla de hechos agrupada por producto. Por ejemplo: Producto A → 1,200 unidades, Producto B → 850 unidades, Producto C → 2,300 unidades, etc.</t>
+          <t>Las unidades vendidas por producto se obtienen sumando la columna 'quantity' de la tabla de hechos agrupada por producto. Por ejemplo, el Producto A vendió 1,200 unidades, el Producto B vendió 980 unidades, etc.</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr"/>
@@ -1143,7 +1139,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita la suma de unidades vendidas agrupadas por producto. La tabla de hechos 'fact_sales_demo_genie' contiene la columna 'quantity' (unidades vendidas) y la llave foránea 'product_id'. La dimensión 'dim_product_demo_genie' contiene los atributos descriptivos del producto (nombre, marca, tipo). Un simple JOIN entre ambas tablas y un GROUP BY sobre product_id/product_name con SUM(quantity) responde completamente la pregunta. No hay ambigüedad ni datos faltantes.</t>
+          <t>La pregunta solicita la suma de unidades vendidas agrupadas por producto. La tabla de hechos 'fact_sales_demo_genie' contiene la columna 'quantity' (unidades vendidas) y la clave foránea 'product_id'. La dimensión 'dim_product_demo_genie' provee los atributos descriptivos del producto (nombre, marca, tipo). Un simple JOIN y un SUM(quantity) GROUP BY product_id/product_name es suficiente para responder la pregunta de forma completa y precisa.</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -1185,7 +1181,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr"/>
       <c r="F30" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1227,7 +1223,7 @@
       <c r="C31" s="11" t="inlineStr"/>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>El total de órdenes realizadas se obtiene contando los valores distintos de order_id en la tabla de hechos de ventas. Por ejemplo, si existen 15,000 valores únicos de order_id, entonces se realizaron 15,000 órdenes en total.</t>
+          <t>El total de órdenes realizadas se obtiene contando los valores distintos de order_id en la tabla de hechos de ventas. Por ejemplo, si hubiera 1,500 órdenes únicas registradas, la respuesta sería: 'Se realizaron 1,500 órdenes en total.'</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr"/>
@@ -1241,7 +1237,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita el conteo total de órdenes. La tabla fact_sales_demo_genie contiene la columna order_id, que identifica cada orden. Dado que una orden puede tener múltiples líneas de producto (y por tanto múltiples filas con el mismo order_id), se debe usar COUNT(DISTINCT order_id) para obtener el número real de órdenes únicas. No se requieren joins adicionales ni información de otras tablas para responder esta pregunta.</t>
+          <t>La pregunta solicita el conteo total de órdenes. La tabla fact_sales_demo_genie contiene la columna order_id, que identifica cada orden. Dado que una orden puede tener múltiples líneas de producto (line_number), se debe usar COUNT(DISTINCT order_id) para evitar duplicados y obtener el número real de órdenes únicas. No se requieren joins adicionales ni información de otras tablas para responder esta pregunta.</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -1263,7 +1259,7 @@
       <c r="C32" s="11" t="inlineStr"/>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Los 10 clientes con mayores ventas brutas son aquellos cuya suma de gross_sales en la tabla de hechos es más alta. Por ejemplo, el cliente con mayor venta bruta podría ser 'Cliente A' con $X millones, seguido de 'Cliente B' con $Y millones, y así sucesivamente hasta completar el top 10.</t>
+          <t>Los 10 clientes con mayores ventas brutas son aquellos cuya suma de gross_sales en la tabla de hechos es más alta. Por ejemplo, el cliente con mayor venta bruta podría ser 'Cliente A' con $X,XXX,XXX en ventas brutas, seguido de 'Cliente B', 'Cliente C', etc., hasta completar el top 10.</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
@@ -1277,7 +1273,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita los 10 clientes con mayores ventas brutas. La tabla fact_sales_demo_genie contiene la columna gross_sales y customer_id, y la tabla dim_customer_demo_genie contiene el nombre del cliente (customer_name) junto con su identificador (customer_id). Con un simple JOIN entre ambas tablas, una agregación SUM sobre gross_sales agrupada por cliente, y un ORDER BY DESC con LIMIT 10, se puede responder la pregunta de forma completa y precisa. No hay ambigüedad ni datos faltantes.</t>
+          <t>La pregunta solicita los 10 clientes con mayores ventas brutas. La tabla fact_sales_demo_genie contiene la columna gross_sales y customer_id, lo que permite agregar las ventas brutas por cliente. La tabla dim_customer_demo_genie proporciona el nombre del cliente (customer_name) mediante un JOIN sobre customer_id. No existe ninguna ambigüedad: 'ventas brutas' mapea directamente a la columna gross_sales, y 'top 10' se resuelve con ORDER BY DESC + LIMIT 10. Todos los datos necesarios están disponibles.</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
@@ -1288,7 +1284,7 @@
     SUM(f.gross_sales) AS total_gross_sales
 FROM
     brz_dev.default.fact_sales_demo_genie f
-    JOIN brz_dev.default.dim_customer_demo_genie c
+    INNER JOIN brz_dev.default.dim_customer_demo_genie c
         ON f.customer_id = c.customer_id
 GROUP BY
     c.customer_id,
@@ -1311,7 +1307,7 @@
       <c r="C33" s="11" t="inlineStr"/>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>La diferencia entre ventas brutas y ventas netas (es decir, el total de descuentos aplicados) por año sería, por ejemplo: en 2022 las ventas brutas fueron $5,000,000, las ventas netas $4,500,000 y la diferencia (descuentos) fue de $500,000; en 2023 las ventas brutas fueron $6,200,000, las ventas netas $5,600,000 y la diferencia fue de $600,000. (Los valores exactos dependen de los datos reales en la tabla.)</t>
+          <t>La diferencia entre ventas brutas y ventas netas por año corresponde al total de descuentos aplicados en cada período. Por ejemplo, en 2023 las ventas brutas podrían ser $10,000,000, las ventas netas $9,200,000 y la diferencia (descuentos totales) $800,000. Esta diferencia equivale directamente a la suma de la columna 'discount' agrupada por año.</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr"/>
@@ -1325,7 +1321,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita la diferencia entre ventas brutas (gross_sales) y ventas netas (net_sales) agrupada por año. Ambas métricas existen directamente en la tabla de hechos 'fact_sales_demo_genie'. El año se obtiene haciendo un JOIN con 'dim_date_demo_genie' usando la clave 'date_id'. La diferencia entre ambas columnas equivale al descuento total aplicado, que también está disponible en la columna 'discount'. No hay ambigüedad ni datos faltantes; la pregunta es completamente respondible con las tablas disponibles.</t>
+          <t>La pregunta solicita la diferencia entre ventas brutas (gross_sales) y ventas netas (net_sales) agrupada por año. Ambas métricas existen directamente en la tabla de hechos 'fact_sales_demo_genie'. El año se obtiene uniendo con 'dim_date_demo_genie' a través de la clave 'date_id'. No hay ambigüedad: la diferencia es una resta aritmética estándar (gross_sales - net_sales), que además coincide con la columna 'discount'. La consulta es completamente derivable con los datos disponibles.</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -1333,14 +1329,16 @@
           <t>SELECT
     d.year,
     SUM(f.gross_sales)                        AS total_gross_sales,
-    SUM(f.net_sales)                           AS total_net_sales,
-    SUM(f.gross_sales) - SUM(f.net_sales)      AS difference_gross_vs_net,
-    SUM(f.discount)                            AS total_discount
+    SUM(f.net_sales)                          AS total_net_sales,
+    SUM(f.gross_sales) - SUM(f.net_sales)     AS difference_gross_vs_net,
+    SUM(f.discount)                           AS total_discount
 FROM brz_dev.default.fact_sales_demo_genie f
 JOIN brz_dev.default.dim_date_demo_genie d
     ON f.date_id = d.date_id
-GROUP BY d.year
-ORDER BY d.year;</t>
+GROUP BY
+    d.year
+ORDER BY
+    d.year;</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1354,7 @@
       <c r="C34" s="11" t="inlineStr"/>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>En el último año (2024, por ejemplo), las unidades vendidas por mes fueron: Enero: 12,500 unidades, Febrero: 11,800 unidades, Marzo: 13,200 unidades, ... (los valores exactos dependerán de los datos reales en la tabla).</t>
+          <t>En el último año (2024, por ejemplo), las unidades vendidas por mes fueron: Enero: 12,500, Febrero: 11,800, Marzo: 13,200, Abril: 14,000, Mayo: 13,750, Junio: 15,100, Julio: 14,300, Agosto: 13,900, Septiembre: 12,600, Octubre: 14,800, Noviembre: 16,200, Diciembre: 17,500. (Valores hipotéticos ilustrativos.)</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr"/>
@@ -1410,7 +1408,7 @@
       <c r="C35" s="11" t="inlineStr"/>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Los productos con un descuento promedio mayor al 10% son aquellos cuyo promedio de la columna 'discount' en la tabla de hechos supera el 10% del valor bruto de venta (gross_sales). Por ejemplo, podrían ser productos como 'Producto A' con un descuento promedio del 12%, 'Producto B' con 15%, etc. La lista exacta depende de los datos reales.</t>
+          <t>Los productos con un descuento promedio mayor al 10% son aquellos cuyo promedio de la columna 'discount' en la tabla de hechos supera el 10% del valor bruto de venta (gross_sales). Por ejemplo, podrían ser productos como 'Producto A' con un descuento promedio del 12%, 'Producto B' con 15%, etc. La consulta calculará AVG(discount/gross_sales) por producto y filtrará los que superen el 10%.</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr"/>
@@ -1424,7 +1422,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita productos cuyo descuento promedio supere el 10%. La tabla 'fact_sales_demo_genie' contiene las columnas 'discount' y 'gross_sales', lo que permite calcular el porcentaje de descuento promedio por producto (discount / gross_sales * 100). La tabla 'dim_product_demo_genie' proporciona los atributos descriptivos del producto (nombre, marca, tipo, fabricante). Se asume que el '10%' se refiere al porcentaje del descuento respecto al valor bruto de venta, que es la interpretación más estándar en contextos comerciales. El JOIN entre ambas tablas se realiza mediante product_id. La consulta agrupa por producto, calcula el porcentaje promedio de descuento y filtra aquellos que superan el 10%.</t>
+          <t>La pregunta solicita productos cuyo descuento promedio supere el 10%. La tabla fact_sales_demo_genie contiene las columnas 'discount' y 'gross_sales', lo que permite calcular el porcentaje de descuento como (discount / gross_sales) * 100. Uniendo con dim_product_demo_genie se obtiene el nombre y características del producto. La condición HAVING filtra aquellos con promedio mayor al 10%. La única consideración es que 'descuento promedio mayor al 10%' se interpreta como el porcentaje del descuento respecto al valor bruto, lo cual es la interpretación estándar de negocio y es completamente derivable con SQL estándar.</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -1435,13 +1433,13 @@
     p.brand,
     p.product_type,
     p.manufacturer,
-    AVG(f.discount) AS avg_discount,
-    AVG(f.gross_sales) AS avg_gross_sales,
-    AVG(f.discount / NULLIF(f.gross_sales, 0)) * 100 AS avg_discount_pct
+    ROUND(AVG(f.discount / NULLIF(f.gross_sales, 0)) * 100, 2) AS avg_discount_pct
 FROM
     brz_dev.default.fact_sales_demo_genie f
     JOIN brz_dev.default.dim_product_demo_genie p
         ON f.product_id = p.product_id
+WHERE
+    f.gross_sales &gt; 0
 GROUP BY
     p.product_id,
     p.product_name,
@@ -1467,7 +1465,7 @@
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>El ingreso neto promedio por orden es el resultado de dividir la suma total de net_sales entre el número de órdenes únicas (order_id). Por ejemplo, si la suma total de net_sales es $10,000,000 y existen 500 órdenes únicas, el ingreso neto promedio por orden sería $20,000.</t>
+          <t>El ingreso neto promedio por orden es el resultado de dividir la suma total de net_sales entre el número de órdenes únicas (order_id). Por ejemplo, si la suma total de net_sales es $10,000,000 y existen 500 órdenes únicas, el ingreso neto promedio por orden sería de $20,000.</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr"/>
@@ -1481,7 +1479,7 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>La pregunta solicita el ingreso neto promedio por orden. La tabla fact_sales_demo_genie contiene tanto 'net_sales' (valor neto de la venta) como 'order_id' (identificador de la orden). Dado que una orden puede tener múltiples líneas de producto, el ingreso neto por orden se calcula sumando net_sales agrupado por order_id, y luego promediando esos totales. Esto es equivalente a dividir la suma total de net_sales entre el número de órdenes únicas (COUNT DISTINCT order_id). No se requieren joins adicionales ni existe ambigüedad en la definición del indicador.</t>
+          <t>La pregunta solicita el ingreso neto promedio por orden. La tabla fact_sales_demo_genie contiene tanto 'net_sales' (valor neto de la venta) como 'order_id' (identificador de la orden). Dado que una orden puede tener múltiples líneas de producto, el ingreso neto por orden se calcula sumando el net_sales de todas las líneas de una misma orden y luego promediando entre todas las órdenes únicas. Esto se logra dividiendo la suma total de net_sales entre el conteo de order_id distintos. No se requieren joins adicionales ni existe ambigüedad en la definición del denominador (orden = order_id único).</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
